--- a/OR/ue01/excel_solver.xlsx
+++ b/OR/ue01/excel_solver.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29912"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEC76549-1C84-47AA-A128-057AE9476267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1B5B918D-AB3D-4D89-A879-D4F5FA19FC9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <definedName name="solver_rhs2" localSheetId="0" hidden="1">Sheet1!$H$22</definedName>
     <definedName name="solver_rhs3" localSheetId="0" hidden="1">Sheet1!$H$12</definedName>
     <definedName name="solver_rxc1" localSheetId="0" hidden="1">1</definedName>
-    <definedName name="solver_rxc2" localSheetId="0" hidden="1">0</definedName>
+    <definedName name="solver_rxc2" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_rxc3" localSheetId="0" hidden="1">0</definedName>
     <definedName name="solver_rxv" localSheetId="0" hidden="1">1</definedName>
     <definedName name="solver_typ" localSheetId="0" hidden="1">1</definedName>
@@ -230,9 +230,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
@@ -248,16 +245,19 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -611,15 +611,15 @@
       <c r="B2" s="1"/>
     </row>
     <row r="3" spans="2:8">
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="2" t="s">
@@ -636,146 +636,146 @@
       <c r="H4" s="5"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7" t="s">
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="8"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="7"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="6"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7">
+      <c r="B6" s="18"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6">
         <v>10</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="6">
         <v>20</v>
       </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="8"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="7"/>
     </row>
     <row r="7" spans="2:8">
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="8"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="7"/>
     </row>
     <row r="8" spans="2:8">
-      <c r="B8" s="6"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="9">
+      <c r="B8" s="18"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="8">
         <v>30</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="8">
         <v>60</v>
       </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="8"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="7"/>
     </row>
     <row r="9" spans="2:8">
-      <c r="B9" s="10"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="7"/>
     </row>
     <row r="10" spans="2:8">
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7">
+      <c r="C10" s="6"/>
+      <c r="D10" s="6">
         <v>1</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>1</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="10">
         <f>D10*D8+E10*E8</f>
         <v>90</v>
       </c>
-      <c r="G10" s="7" t="s">
+      <c r="G10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="7">
         <v>100</v>
       </c>
     </row>
     <row r="11" spans="2:8">
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7">
+      <c r="C11" s="6"/>
+      <c r="D11" s="6">
         <v>6</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="6">
         <v>9</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="10">
         <f>D11*D8+E11*E8</f>
         <v>720</v>
       </c>
-      <c r="G11" s="7" t="s">
+      <c r="G11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="7">
         <v>720</v>
       </c>
     </row>
     <row r="12" spans="2:8">
-      <c r="B12" s="12" t="s">
+      <c r="B12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12">
         <v>0</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="12">
         <v>1</v>
       </c>
-      <c r="F12" s="14">
+      <c r="F12" s="13">
         <f>D12*D8+E12*E8</f>
         <v>60</v>
       </c>
-      <c r="G12" s="13" t="s">
+      <c r="G12" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="15">
+      <c r="H12" s="14">
         <v>60</v>
       </c>
     </row>
     <row r="14" spans="2:8">
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
     </row>
     <row r="15" spans="2:8">
       <c r="B15" s="2" t="s">
@@ -784,7 +784,7 @@
       <c r="C15" s="3"/>
       <c r="D15" s="4">
         <f>D19*D17+E19*E17</f>
-        <v>120000</v>
+        <v>112500</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
@@ -792,111 +792,111 @@
       <c r="H15" s="5"/>
     </row>
     <row r="16" spans="2:8">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="8"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="7"/>
     </row>
     <row r="17" spans="2:8">
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7">
+      <c r="B17" s="18"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6">
         <v>2000</v>
       </c>
-      <c r="E17" s="7">
+      <c r="E17" s="6">
         <v>3000</v>
       </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="7"/>
     </row>
     <row r="18" spans="2:8">
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="8"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="7"/>
     </row>
     <row r="19" spans="2:8">
-      <c r="B19" s="6"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="9">
-        <v>60</v>
-      </c>
-      <c r="E19" s="9">
-        <v>0</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="8">
+        <v>22.500000000000004</v>
+      </c>
+      <c r="E19" s="8">
+        <v>22.499999999999996</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="7"/>
     </row>
     <row r="20" spans="2:8">
-      <c r="B20" s="10"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="6"/>
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8">
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7">
+      <c r="C21" s="6"/>
+      <c r="D21" s="6">
         <v>3</v>
       </c>
-      <c r="E21" s="7">
+      <c r="E21" s="6">
         <v>5</v>
       </c>
-      <c r="F21" s="18">
+      <c r="F21" s="15">
         <f>D21*D19+E21*E19</f>
         <v>180</v>
       </c>
-      <c r="G21" s="7" t="s">
+      <c r="G21" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="7">
         <v>180</v>
       </c>
     </row>
     <row r="22" spans="2:8">
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12">
         <v>3</v>
       </c>
-      <c r="E22" s="13">
+      <c r="E22" s="12">
         <v>3</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="16">
         <f>D22*D19+E22*E19</f>
-        <v>180</v>
-      </c>
-      <c r="G22" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="H22" s="15">
+      <c r="H22" s="14">
         <v>135</v>
       </c>
     </row>
